--- a/Avantis/Avantis.xlsx
+++ b/Avantis/Avantis.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Avantis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1617" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73794820-745C-47CF-9255-5D39F5CAC306}"/>
+  <xr:revisionPtr revIDLastSave="2053" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{442B555B-36A4-4EEA-A1E1-142A46E156D6}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVUV" sheetId="17" r:id="rId1"/>
-    <sheet name="AVLV" sheetId="24" r:id="rId2"/>
-    <sheet name="AVIV" sheetId="26" r:id="rId3"/>
-    <sheet name="AVDV" sheetId="18" r:id="rId4"/>
-    <sheet name="AVES" sheetId="25" r:id="rId5"/>
+    <sheet name="AVMV" sheetId="27" r:id="rId2"/>
+    <sheet name="AVLV" sheetId="24" r:id="rId3"/>
+    <sheet name="AVIV" sheetId="26" r:id="rId4"/>
+    <sheet name="AVDV" sheetId="18" r:id="rId5"/>
+    <sheet name="AVES" sheetId="25" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="29">
-  <si>
-    <t>Dividend income (net)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="32">
   <si>
     <t>Net asset value end of year</t>
   </si>
@@ -78,9 +76,6 @@
   </si>
   <si>
     <t>Lending income</t>
-  </si>
-  <si>
-    <t>Fees</t>
   </si>
   <si>
     <t>Lending income %</t>
@@ -127,6 +122,21 @@
   <si>
     <t>Total costs</t>
   </si>
+  <si>
+    <t>Management fees</t>
+  </si>
+  <si>
+    <t>Avantis U.S. Mid Cap Value ETF (AVMV)</t>
+  </si>
+  <si>
+    <t>Dividend income (gross)</t>
+  </si>
+  <si>
+    <t>Dividend income (net/gross)</t>
+  </si>
+  <si>
+    <t>Since 2025 gross dividends are reported</t>
+  </si>
 </sst>
 </file>
 
@@ -138,7 +148,7 @@
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +175,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -199,7 +217,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -227,6 +245,8 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -510,35 +530,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A50C80A-B9F0-42B2-B14F-324E5B39F7D5}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="34.42578125" customWidth="1"/>
+    <col min="3" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="7"/>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="7"/>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2020</v>
       </c>
@@ -551,13 +573,19 @@
       <c r="E3" s="1">
         <v>2023</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="5">
         <v>355298485</v>
@@ -571,14 +599,20 @@
       <c r="E4" s="5">
         <v>6820449176</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F4" s="5">
+        <v>13186674878</v>
+      </c>
+      <c r="G4" s="5">
+        <v>18272384642</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5">
         <v>317911</v>
@@ -592,17 +626,23 @@
       <c r="E5" s="5">
         <v>13051606</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" s="5">
+        <v>24182002</v>
+      </c>
+      <c r="G5" s="5">
+        <v>38129751</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="4">
-        <f>0.25%*H6</f>
+        <f>0.25%*J6</f>
         <v>2.3360655737704921E-3</v>
       </c>
       <c r="C6" s="4">
@@ -615,20 +655,26 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F6" s="4">
-        <f>AVERAGE(B6:E6)</f>
-        <v>2.4590163934426232E-3</v>
-      </c>
-      <c r="H6" s="17">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="H6" s="4">
+        <f>AVERAGE(C6:G6)</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="J6" s="17">
         <f>342/366</f>
         <v>0.93442622950819676</v>
       </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5">
         <f>B5/B6</f>
@@ -646,18 +692,28 @@
         <f>E5/E6</f>
         <v>5220642400</v>
       </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F7" s="5">
+        <f t="shared" ref="F7:G7" si="0">F5/F6</f>
+        <v>9672800800</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>15251900400</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5">
         <v>7410</v>
@@ -671,14 +727,20 @@
       <c r="E9" s="5">
         <v>787708</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="5">
+        <v>202076</v>
+      </c>
+      <c r="G9" s="5">
+        <v>547357</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
-        <f>(B9/B7)/H6</f>
+        <f>(B9/B7)/J6</f>
         <v>5.8271025538594139E-5</v>
       </c>
       <c r="C10" s="2">
@@ -693,17 +755,25 @@
         <f>E9/E7</f>
         <v>1.5088334722945207E-4</v>
       </c>
-      <c r="F10" s="4">
-        <f>AVERAGE(B10:E10)</f>
-        <v>8.5978943650084135E-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F10" s="2">
+        <f t="shared" ref="F10:G10" si="1">F9/F7</f>
+        <v>2.0891156985265323E-5</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>3.588779008811256E-5</v>
+      </c>
+      <c r="H10" s="4">
+        <f>AVERAGE(C10:G10)</f>
+        <v>6.8484739227024053E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5">
         <v>2685568</v>
@@ -717,11 +787,20 @@
       <c r="E12" s="5">
         <v>120567369</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F12" s="5">
+        <v>204530618</v>
+      </c>
+      <c r="G12" s="5">
+        <v>327341895</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="J12" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="5">
         <v>4931</v>
@@ -735,36 +814,50 @@
       <c r="E13" s="5">
         <v>119999</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F13" s="5">
+        <v>348472</v>
+      </c>
+      <c r="G13" s="5">
+        <v>492547</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="9">
-        <f t="shared" ref="B14:C14" si="0">B13/(B12+B13)</f>
+        <f t="shared" ref="B14:F14" si="2">B13/(B12+B13)</f>
         <v>1.8327455241574147E-3</v>
       </c>
       <c r="C14" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2759472370738145E-3</v>
       </c>
       <c r="D14" s="9">
-        <f t="shared" ref="D14:E14" si="1">D13/(D12+D13)</f>
+        <f t="shared" si="2"/>
         <v>1.2621326811190995E-3</v>
       </c>
       <c r="E14" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.942962713380243E-4</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F14" s="9">
+        <f t="shared" si="2"/>
+        <v>1.7008665940482263E-3</v>
+      </c>
+      <c r="G14" s="9">
+        <f>G13/G12</f>
+        <v>1.5046867129549671E-3</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
-        <f>((B12+B13)/B7)/H6</f>
+        <f>((B12+B13)/B7)/J6</f>
         <v>2.1157643176863965E-2</v>
       </c>
       <c r="C15" s="9">
@@ -779,14 +872,22 @@
         <f>(E12+E13)/E7</f>
         <v>2.3117340502004122E-2</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F15" s="9">
+        <f>(F12+F13)/F7</f>
+        <v>2.1180947921516174E-2</v>
+      </c>
+      <c r="G15" s="9">
+        <f>G12/G7</f>
+        <v>2.146236773222044E-2</v>
+      </c>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="9">
-        <f>(B13/B7)/H6</f>
+        <f>(B13/B7)/J6</f>
         <v>3.87765758341171E-5</v>
       </c>
       <c r="C16" s="9">
@@ -801,21 +902,31 @@
         <f>E13/E7</f>
         <v>2.298548546439419E-5</v>
       </c>
-      <c r="F16" s="4">
-        <f>AVERAGE(B16:E16)</f>
-        <v>2.8048345638917311E-5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="9">
+        <f>F13/F7</f>
+        <v>3.6025966749982071E-5</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" ref="G16" si="3">G13/G7</f>
+        <v>3.2294139555225523E-5</v>
+      </c>
+      <c r="H16" s="4">
+        <f>AVERAGE(C16:G16)</f>
+        <v>2.834738260535195E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="14">
         <v>0.2</v>
@@ -827,16 +938,22 @@
         <v>0.24</v>
       </c>
       <c r="E18" s="14">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F18" s="14">
-        <f>AVERAGE(B18:E18)</f>
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.04</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="H18" s="4">
+        <f>AVERAGE(C18:G18)</f>
+        <v>0.12600000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5">
         <f>28342</f>
@@ -852,14 +969,20 @@
       <c r="E19" s="5">
         <v>274645</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="5">
+        <v>387532</v>
+      </c>
+      <c r="G19" s="5">
+        <v>665737</v>
+      </c>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4">
-        <f>(B19/B7)/H6</f>
+        <f>(B19/B7)/J6</f>
         <v>2.2287684288999123E-4</v>
       </c>
       <c r="C20" s="3">
@@ -874,238 +997,299 @@
         <f>E19/E7</f>
         <v>5.2607510523992221E-5</v>
       </c>
-      <c r="F20" s="4">
-        <f>AVERAGE(B20:E20)</f>
-        <v>1.387665112199256E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="19">
-        <f>B3</f>
-        <v>2020</v>
-      </c>
-      <c r="C24" s="19">
+      <c r="F20" s="3">
+        <f t="shared" ref="F20:G20" si="4">F19/F7</f>
+        <v>4.0064093948879832E-5</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="4"/>
+        <v>4.3649445809389101E-5</v>
+      </c>
+      <c r="H20" s="4">
+        <f>AVERAGE(C20:G20)</f>
+        <v>8.3180548349596022E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19">
         <f>C3</f>
         <v>2021</v>
       </c>
-      <c r="D24" s="19">
-        <f>D3</f>
+      <c r="D25" s="19">
+        <f t="shared" ref="D25:G25" si="5">D3</f>
         <v>2022</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E25" s="19">
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="str">
+      <c r="F25" s="19">
+        <f t="shared" si="5"/>
+        <v>2024</v>
+      </c>
+      <c r="G25" s="19">
+        <f t="shared" si="5"/>
+        <v>2025</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
         <f>A10</f>
         <v>Lending income %</v>
       </c>
-      <c r="B25" s="4">
-        <f>B10</f>
-        <v>5.8271025538594139E-5</v>
-      </c>
-      <c r="C25" s="4">
-        <f t="shared" ref="C25:E25" si="2">C10</f>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4">
+        <f t="shared" ref="C26:G26" si="6">C10</f>
         <v>1.0554648854576879E-4</v>
       </c>
-      <c r="D25" s="4">
-        <f t="shared" si="2"/>
+      <c r="D26" s="4">
+        <f t="shared" si="6"/>
         <v>2.9214913286521525E-5</v>
       </c>
-      <c r="E25" s="3">
-        <f t="shared" si="2"/>
+      <c r="E26" s="3">
+        <f t="shared" si="6"/>
         <v>1.5088334722945207E-4</v>
       </c>
-      <c r="F25" s="9">
-        <f>AVERAGE(B25:E25)</f>
-        <v>8.5978943650084135E-5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="str">
+      <c r="F26" s="3">
+        <f t="shared" si="6"/>
+        <v>2.0891156985265323E-5</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="6"/>
+        <v>3.588779008811256E-5</v>
+      </c>
+      <c r="H26" s="9">
+        <f>AVERAGE(C26:G26)</f>
+        <v>6.8484739227024053E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
         <f>A20</f>
         <v>Brokerage commissions %</v>
       </c>
-      <c r="B26" s="3">
-        <f>B20</f>
-        <v>2.2287684288999123E-4</v>
-      </c>
-      <c r="C26" s="3">
-        <f t="shared" ref="C26:E26" si="3">C20</f>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3">
+        <f>C20</f>
         <v>1.6838430470042957E-4</v>
       </c>
-      <c r="D26" s="3">
-        <f t="shared" si="3"/>
+      <c r="D27" s="3">
+        <f>D20</f>
         <v>1.1119738676528936E-4</v>
       </c>
-      <c r="E26" s="3">
-        <f t="shared" si="3"/>
+      <c r="E27" s="3">
+        <f>E20</f>
         <v>5.2607510523992221E-5</v>
       </c>
-      <c r="F26" s="9">
-        <f t="shared" ref="F26:F29" si="4">AVERAGE(B26:E26)</f>
-        <v>1.387665112199256E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="str">
+      <c r="F27" s="3">
+        <f>F20</f>
+        <v>4.0064093948879832E-5</v>
+      </c>
+      <c r="G27" s="3">
+        <f>G20</f>
+        <v>4.3649445809389101E-5</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" ref="H27:H30" si="7">AVERAGE(C27:G27)</f>
+        <v>8.3180548349596022E-5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="str">
         <f>A15</f>
         <v>Dividend (gross)</v>
       </c>
-      <c r="B28" s="4">
-        <f>B15</f>
-        <v>2.1157643176863965E-2</v>
-      </c>
-      <c r="C28" s="4">
-        <f t="shared" ref="C28:E28" si="5">C15</f>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4">
+        <f>C15</f>
         <v>1.9605053660907076E-2</v>
       </c>
-      <c r="D28" s="4">
-        <f t="shared" si="5"/>
+      <c r="D29" s="4">
+        <f>D15</f>
         <v>2.0137587423299855E-2</v>
       </c>
-      <c r="E28" s="4">
-        <f t="shared" si="5"/>
+      <c r="E29" s="4">
+        <f>E15</f>
         <v>2.3117340502004122E-2</v>
       </c>
-      <c r="F28" s="9">
-        <f t="shared" si="4"/>
-        <v>2.1004406190768755E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="str">
+      <c r="F29" s="4">
+        <f>F15</f>
+        <v>2.1180947921516174E-2</v>
+      </c>
+      <c r="G29" s="4">
+        <f>G15</f>
+        <v>2.146236773222044E-2</v>
+      </c>
+      <c r="H29" s="9">
+        <f t="shared" si="7"/>
+        <v>2.1100659447989535E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="str">
         <f>A18</f>
         <v>Turnover</v>
       </c>
-      <c r="B29" s="14">
-        <f>B18</f>
-        <v>0.2</v>
-      </c>
-      <c r="C29" s="14">
-        <f t="shared" ref="C29:E29" si="6">C18</f>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14">
+        <f>C18</f>
         <v>0.22</v>
       </c>
-      <c r="D29" s="14">
-        <f t="shared" si="6"/>
+      <c r="D30" s="14">
+        <f>D18</f>
         <v>0.24</v>
       </c>
-      <c r="E29" s="14">
-        <f t="shared" si="6"/>
-        <v>0.09</v>
-      </c>
-      <c r="F29" s="20">
-        <f t="shared" si="4"/>
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4">
-        <f>E6-F10+F20</f>
-        <v>2.5527875675698413E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
+      <c r="E30" s="14">
+        <f>E18</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F30" s="14">
+        <f>F18</f>
+        <v>0.04</v>
+      </c>
+      <c r="G30" s="14">
+        <f>G18</f>
+        <v>0.06</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="7"/>
+        <v>0.12600000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4">
+        <f>H6-H10+H20</f>
+        <v>2.5146958091225723E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1114,287 +1298,317 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D94FFC8-24A2-4765-AFE3-C706492DE4CB}">
-  <dimension ref="A1:F49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A38D820-4041-4436-94DD-656E78B82070}">
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="2" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E2" s="1" t="s">
-        <v>16</v>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
+        <v>2025</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="5">
-        <v>494954605</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="E4" s="17">
-        <f>345/366</f>
-        <v>0.94262295081967218</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
+        <v>264174534</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="1"/>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5">
-        <v>276288</v>
-      </c>
-      <c r="C5" s="1"/>
+        <v>292195</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="4">
-        <f>0.15%*E4</f>
-        <v>1.4139344262295082E-3</v>
-      </c>
-      <c r="C6" s="4">
-        <f>AVERAGE(B6:B6)</f>
-        <v>1.4139344262295082E-3</v>
-      </c>
+        <v>2E-3</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <f>AVERAGE(B6)</f>
+        <v>2E-3</v>
+      </c>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5">
         <f>B5/B6</f>
-        <v>195403686.95652175</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>146097500</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
-      <c r="C8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5">
-        <v>2512</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>181</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="18">
-        <f>(B9/B7)/E4</f>
-        <v>1.363794301598332E-5</v>
-      </c>
-      <c r="C10" s="4">
-        <f>AVERAGE(B10:B10)</f>
-        <v>1.363794301598332E-5</v>
+        <f>B9/B7</f>
+        <v>1.2388986806755763E-6</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="4">
+        <f>AVERAGE(B10)</f>
+        <v>1.2388986806755763E-6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B12" s="5">
-        <v>4766113</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>2612131</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="5">
-        <v>517</v>
-      </c>
-      <c r="C13" s="4"/>
+        <v>925</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="9">
-        <f>B13/(B12+B13)</f>
-        <v>1.0846237278748298E-4</v>
-      </c>
-      <c r="C14" s="4"/>
+        <f>B13/B12</f>
+        <v>3.5411700255461921E-4</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
-        <f>((B12+B13)/B7)/E4</f>
-        <v>2.5878594075747045E-2</v>
-      </c>
-      <c r="C15" s="4"/>
+        <f>B12/B7</f>
+        <v>1.7879368230120297E-2</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="10">
-        <f>(B13/B7)/E4</f>
-        <v>2.8068537178596244E-6</v>
-      </c>
-      <c r="C16" s="4">
-        <f>AVERAGE(B16:B16)</f>
-        <v>2.8068537178596244E-6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B16" s="21">
+        <f>B13/B7</f>
+        <v>6.3313882852204867E-6</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="4">
+        <f>AVERAGE(B16)</f>
+        <v>6.3313882852204867E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="9"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="14">
-        <v>0.23</v>
-      </c>
-      <c r="C18" s="14">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="4">
         <f>AVERAGE(B18)</f>
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5">
-        <v>7792</v>
-      </c>
-      <c r="C19" s="14"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7833</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4">
-        <f>(B19/B7)/E4</f>
-        <v>4.2303683113273106E-5</v>
-      </c>
-      <c r="C20" s="4">
-        <f>AVERAGE(B20:B20)</f>
-        <v>4.2303683113273106E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <f>B19/B7</f>
+        <v>5.361488047365629E-5</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4">
+        <f>AVERAGE(B20)</f>
+        <v>5.361488047365629E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="4"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="20"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
       <c r="B38" s="11"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="11"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="11"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="11"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="11"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="11"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="11"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="11"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="11"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="11"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
+      <c r="C42" s="11"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1403,287 +1617,594 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFAC02E-C033-44C9-A725-F88F03ADB5EB}">
-  <dimension ref="A1:F49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D94FFC8-24A2-4765-AFE3-C706492DE4CB}">
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="2" max="6" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2022</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5">
+        <v>494954605</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1483946663</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4348250092</v>
+      </c>
+      <c r="E4" s="5">
+        <v>8199763307</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="H4" s="17">
+        <f>345/366</f>
+        <v>0.94262295081967218</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="5">
+        <v>276288</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1363098</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4100779</v>
+      </c>
+      <c r="E5" s="5">
+        <v>9073193</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5">
-        <v>60391814</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="E4" s="17">
-        <f>338/366</f>
-        <v>0.92349726775956287</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5">
-        <v>65598</v>
-      </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" s="4">
+        <f>0.15%*H4</f>
+        <v>1.4139344262295082E-3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.5E-3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.5E-3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1.5E-3</v>
+      </c>
+      <c r="F6" s="4">
+        <f>AVERAGE(C6:E6)</f>
+        <v>1.5000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>2</v>
-      </c>
-      <c r="B6" s="4">
-        <f>0.25%*E4</f>
-        <v>2.308743169398907E-3</v>
-      </c>
-      <c r="C6" s="4">
-        <f>AVERAGE(B6:B6)</f>
-        <v>2.308743169398907E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
       </c>
       <c r="B7" s="5">
         <f>B5/B6</f>
-        <v>28412861.53846154</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>195403686.95652175</v>
+      </c>
+      <c r="C7" s="5">
+        <f t="shared" ref="C7:E7" si="0">C5/C6</f>
+        <v>908732000</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" si="0"/>
+        <v>2733852666.6666665</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>6048795333.333333</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2512</v>
+      </c>
+      <c r="C9" s="5">
+        <v>10235</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3480</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3784</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5">
-        <v>4386</v>
-      </c>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="16">
-        <f>(B9/B7)/E4</f>
-        <v>1.6715448641726883E-4</v>
-      </c>
-      <c r="C10" s="4">
-        <f>AVERAGE(B10:B10)</f>
-        <v>1.6715448641726883E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="18">
+        <f>(B9/B7)/H4</f>
+        <v>1.363794301598332E-5</v>
+      </c>
+      <c r="C10" s="18">
+        <f>C9/C7</f>
+        <v>1.1262946611322149E-5</v>
+      </c>
+      <c r="D10" s="18">
+        <f t="shared" ref="D10:E10" si="1">D9/D7</f>
+        <v>1.2729288752210251E-6</v>
+      </c>
+      <c r="E10" s="18">
+        <f t="shared" si="1"/>
+        <v>6.255791098018085E-7</v>
+      </c>
+      <c r="F10" s="4">
+        <f>AVERAGE(C10:E10)</f>
+        <v>4.3871515321149941E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="5">
+        <v>4766113</v>
+      </c>
+      <c r="C12" s="5">
+        <v>22413361</v>
+      </c>
+      <c r="D12" s="5">
+        <v>56331573</v>
+      </c>
+      <c r="E12" s="5">
+        <v>116050051</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="H12" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5">
+        <v>517</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3990</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20589</v>
+      </c>
+      <c r="E13" s="5">
         <v>0</v>
       </c>
-      <c r="B12" s="5">
-        <v>1270624</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>5</v>
-      </c>
-      <c r="B13" s="5">
-        <v>115881</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>6</v>
       </c>
       <c r="B14" s="9">
         <f>B13/(B12+B13)</f>
-        <v>8.357777288938735E-2</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.0846237278748298E-4</v>
+      </c>
+      <c r="C14" s="9">
+        <f>C13/(C12+C13)</f>
+        <v>1.7798713148578526E-4</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" ref="D14" si="2">D13/(D12+D13)</f>
+        <v>3.6536308935227721E-4</v>
+      </c>
+      <c r="E14" s="9">
+        <f>E13/E12</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
-        <f>((B12+B13)/B7)/E4</f>
-        <v>5.2840978383487294E-2</v>
-      </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <f>((B12+B13)/B7)/H4</f>
+        <v>2.5878594075747045E-2</v>
+      </c>
+      <c r="C15" s="9">
+        <f>(C12+C13)/C7</f>
+        <v>2.4668825352249069E-2</v>
+      </c>
+      <c r="D15" s="9">
+        <f t="shared" ref="D15" si="3">(D12+D13)/D7</f>
+        <v>2.0612728215785345E-2</v>
+      </c>
+      <c r="E15" s="9">
+        <f>E12/E7</f>
+        <v>1.9185646827968941E-2</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="10">
-        <f>(B13/B7)/E4</f>
-        <v>4.4163312905881272E-3</v>
-      </c>
-      <c r="C16" s="4">
-        <f>AVERAGE(B16:B16)</f>
-        <v>4.4163312905881272E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <f>(B13/B7)/H4</f>
+        <v>2.8068537178596244E-6</v>
+      </c>
+      <c r="C16" s="10">
+        <f>C13/C7</f>
+        <v>4.3907334615706278E-6</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" ref="D16:E16" si="4">D13/D7</f>
+        <v>7.5311300608981861E-6</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <f>AVERAGE(C16:E16)</f>
+        <v>3.9739545074896052E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="14">
-        <v>0.47</v>
+        <v>0.23</v>
       </c>
       <c r="C18" s="14">
-        <f>AVERAGE(B18)</f>
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.18</v>
+      </c>
+      <c r="D18" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="E18" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F18" s="4">
+        <f>AVERAGE(C18:E18)</f>
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5">
-        <v>19746</v>
-      </c>
-      <c r="C19" s="14"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7792</v>
+      </c>
+      <c r="C19" s="5">
+        <v>26969</v>
+      </c>
+      <c r="D19" s="5">
+        <v>38252</v>
+      </c>
+      <c r="E19" s="5">
+        <v>58379</v>
+      </c>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4">
-        <f>(B19/B7)/E4</f>
-        <v>7.5253818713985176E-4</v>
+        <f>(B19/B7)/H4</f>
+        <v>4.2303683113273106E-5</v>
       </c>
       <c r="C20" s="4">
-        <f>AVERAGE(B20:B20)</f>
-        <v>7.5253818713985176E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <f>C19/C7</f>
+        <v>2.9677616723082272E-5</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" ref="D20:E20" si="5">D19/D7</f>
+        <v>1.399197567096398E-5</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="5"/>
+        <v>9.6513432481817593E-6</v>
+      </c>
+      <c r="F20" s="4">
+        <f>AVERAGE(C20:E20)</f>
+        <v>1.7773645214076005E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="B23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19">
+        <f>C3</f>
+        <v>2023</v>
+      </c>
+      <c r="D25" s="19">
+        <f t="shared" ref="D25:G25" si="6">D3</f>
+        <v>2024</v>
+      </c>
+      <c r="E25" s="19">
+        <f t="shared" si="6"/>
+        <v>2025</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
+        <f>A10</f>
+        <v>Lending income %</v>
+      </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="3">
+        <f t="shared" ref="C26:G26" si="7">C10</f>
+        <v>1.1262946611322149E-5</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="7"/>
+        <v>1.2729288752210251E-6</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="7"/>
+        <v>6.255791098018085E-7</v>
+      </c>
+      <c r="F26" s="9">
+        <f>AVERAGE(C26:E26)</f>
+        <v>4.3871515321149941E-6</v>
+      </c>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
+        <f>A20</f>
+        <v>Brokerage commissions %</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3">
+        <f>C20</f>
+        <v>2.9677616723082272E-5</v>
+      </c>
+      <c r="D27" s="3">
+        <f>D20</f>
+        <v>1.399197567096398E-5</v>
+      </c>
+      <c r="E27" s="3">
+        <f>E20</f>
+        <v>9.6513432481817593E-6</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" ref="F27:F30" si="8">AVERAGE(C27:E27)</f>
+        <v>1.7773645214076005E-5</v>
+      </c>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="str">
+        <f>A15</f>
+        <v>Dividend (gross)</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4">
+        <f>C15</f>
+        <v>2.4668825352249069E-2</v>
+      </c>
+      <c r="D29" s="4">
+        <f>D15</f>
+        <v>2.0612728215785345E-2</v>
+      </c>
+      <c r="E29" s="4">
+        <f>E15</f>
+        <v>1.9185646827968941E-2</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="8"/>
+        <v>2.1489066798667786E-2</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="str">
+        <f>A18</f>
+        <v>Turnover</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14">
+        <f>C18</f>
+        <v>0.18</v>
+      </c>
+      <c r="D30" s="14">
+        <f>D18</f>
+        <v>0.05</v>
+      </c>
+      <c r="E30" s="14">
+        <f>E18</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="8"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4">
+        <f>F6-F10+F20</f>
+        <v>1.5133864936819612E-3</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="8"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="11"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="11"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="11"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="11"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="11"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="11"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1692,142 +2213,134 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A598ED46-EEA8-4CD3-B87C-CF32F0FABA87}">
-  <dimension ref="A1:I34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFAC02E-C033-44C9-A725-F88F03ADB5EB}">
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="2" max="6" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="7"/>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H2" t="s">
-        <v>10</v>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C3" s="1">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D3" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E3" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="5">
-        <v>274824683</v>
+        <v>60391814</v>
       </c>
       <c r="C4" s="5">
-        <v>1056702827</v>
+        <v>251856063</v>
       </c>
       <c r="D4" s="5">
-        <v>1668508447</v>
+        <v>421630486</v>
       </c>
       <c r="E4" s="5">
-        <v>3452076592</v>
+        <v>831524450</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="17">
+        <f>338/366</f>
+        <v>0.92349726775956287</v>
+      </c>
+      <c r="I4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5">
-        <v>292899</v>
+        <v>65598</v>
       </c>
       <c r="C5" s="5">
-        <v>2087838</v>
+        <v>455526</v>
       </c>
       <c r="D5" s="5">
-        <v>5061317</v>
+        <v>816387</v>
       </c>
       <c r="E5" s="5">
-        <v>9208685</v>
+        <v>1493702</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="4">
-        <f>0.36%*H6</f>
-        <v>3.3639344262295081E-3</v>
+        <f>0.25%*H4</f>
+        <v>2.308743169398907E-3</v>
       </c>
       <c r="C6" s="4">
-        <v>3.5999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="D6" s="4">
-        <v>3.5999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="E6" s="4">
-        <v>3.5999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="F6" s="4">
-        <f>AVERAGE(B6:E6)</f>
-        <v>3.5409836065573765E-3</v>
-      </c>
-      <c r="H6" s="17">
-        <f>342/366</f>
-        <v>0.93442622950819676</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
+        <f>AVERAGE(C6:E6)</f>
+        <v>2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5">
         <f>B5/B6</f>
-        <v>87070365.49707602</v>
+        <v>28412861.53846154</v>
       </c>
       <c r="C7" s="5">
         <f>C5/C6</f>
-        <v>579955000</v>
+        <v>182210400</v>
       </c>
       <c r="D7" s="5">
-        <f>D5/D6</f>
-        <v>1405921388.8888888</v>
+        <f t="shared" ref="D7:E7" si="0">D5/D6</f>
+        <v>326554800</v>
       </c>
       <c r="E7" s="5">
-        <f>E5/E6</f>
-        <v>2557968055.5555558</v>
+        <f t="shared" si="0"/>
+        <v>597480800</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -1840,7 +2353,666 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4386</v>
+      </c>
+      <c r="C9" s="5">
+        <v>67518</v>
+      </c>
+      <c r="D9" s="5">
+        <v>123640</v>
+      </c>
+      <c r="E9" s="5">
+        <v>163552</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>12</v>
+      </c>
+      <c r="B10" s="16">
+        <f>(B9/B7)/H4</f>
+        <v>1.6715448641726883E-4</v>
+      </c>
+      <c r="C10" s="16">
+        <f>C9/C7</f>
+        <v>3.7054965029438493E-4</v>
+      </c>
+      <c r="D10" s="16">
+        <f t="shared" ref="D10:E10" si="1">D9/D7</f>
+        <v>3.7861945376396245E-4</v>
+      </c>
+      <c r="E10" s="16">
+        <f t="shared" si="1"/>
+        <v>2.7373599285533527E-4</v>
+      </c>
+      <c r="F10" s="4">
+        <f>AVERAGE(C10:E10)</f>
+        <v>3.4096836563789418E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1270624</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7936665</v>
+      </c>
+      <c r="D12" s="5">
+        <v>12035617</v>
+      </c>
+      <c r="E12" s="5">
+        <v>23006459</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="H12" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5">
+        <v>115881</v>
+      </c>
+      <c r="C13" s="5">
+        <v>845233</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1347015</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2326251</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="9">
+        <f>B13/(B12+B13)</f>
+        <v>8.357777288938735E-2</v>
+      </c>
+      <c r="C14" s="9">
+        <f t="shared" ref="C14" si="2">C13/(C12+C13)</f>
+        <v>9.6247189388899757E-2</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" ref="D14" si="3">D13/(D12+D13)</f>
+        <v>0.10065396702233163</v>
+      </c>
+      <c r="E14" s="9">
+        <f>E13/E12</f>
+        <v>0.10111295267124767</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9">
+        <f>((B12+B13)/B7)/H4</f>
+        <v>5.2840978383487294E-2</v>
+      </c>
+      <c r="C15" s="9">
+        <f>(C12+C13)/C7</f>
+        <v>4.819646957583102E-2</v>
+      </c>
+      <c r="D15" s="9">
+        <f t="shared" ref="D15:E15" si="4">(D12+D13)/D7</f>
+        <v>4.0981274812068293E-2</v>
+      </c>
+      <c r="E15" s="9">
+        <f>E12/E7</f>
+        <v>3.8505771231477227E-2</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="10">
+        <f>(B13/B7)/H4</f>
+        <v>4.4163312905881272E-3</v>
+      </c>
+      <c r="C16" s="10">
+        <f>C13/C7</f>
+        <v>4.6387747351413532E-3</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" ref="D16:E16" si="5">D13/D7</f>
+        <v>4.1249278834670318E-3</v>
+      </c>
+      <c r="E16" s="10">
+        <f>E13/E7</f>
+        <v>3.893432224098247E-3</v>
+      </c>
+      <c r="F16" s="4">
+        <f>AVERAGE(C16:E16)</f>
+        <v>4.2190449475688774E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0.21</v>
+      </c>
+      <c r="D18" s="14">
+        <v>0.16</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0.11</v>
+      </c>
+      <c r="F18" s="4">
+        <f>AVERAGE(C18:E18)</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5">
+        <v>19746</v>
+      </c>
+      <c r="C19" s="5">
+        <v>67659</v>
+      </c>
+      <c r="D19" s="5">
+        <v>66478</v>
+      </c>
+      <c r="E19" s="5">
+        <v>121698</v>
+      </c>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4">
+        <f>(B19/B7)/H4</f>
+        <v>7.5253818713985176E-4</v>
+      </c>
+      <c r="C20" s="4">
+        <f>C19/C7</f>
+        <v>3.7132348098681522E-4</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" ref="D20:E20" si="6">D19/D7</f>
+        <v>2.0357379527111529E-4</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="6"/>
+        <v>2.0368520628612669E-4</v>
+      </c>
+      <c r="F20" s="4">
+        <f>AVERAGE(C20:E20)</f>
+        <v>2.5952749418135237E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19">
+        <f>C3</f>
+        <v>2023</v>
+      </c>
+      <c r="D25" s="19">
+        <f t="shared" ref="D25:F25" si="7">D3</f>
+        <v>2024</v>
+      </c>
+      <c r="E25" s="19">
+        <f t="shared" si="7"/>
+        <v>2025</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
+        <f>A10</f>
+        <v>Lending income %</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4">
+        <f>C10</f>
+        <v>3.7054965029438493E-4</v>
+      </c>
+      <c r="D26" s="4">
+        <f>D10</f>
+        <v>3.7861945376396245E-4</v>
+      </c>
+      <c r="E26" s="4">
+        <f>E10</f>
+        <v>2.7373599285533527E-4</v>
+      </c>
+      <c r="F26" s="9">
+        <f>AVERAGE(C26:E26)</f>
+        <v>3.4096836563789418E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
+        <f>A16</f>
+        <v>Tax leakage costs</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
+        <f>C16</f>
+        <v>4.6387747351413532E-3</v>
+      </c>
+      <c r="D27" s="4">
+        <f>D16</f>
+        <v>4.1249278834670318E-3</v>
+      </c>
+      <c r="E27" s="4">
+        <f>E16</f>
+        <v>3.893432224098247E-3</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" ref="F27:F32" si="8">AVERAGE(C27:E27)</f>
+        <v>4.2190449475688774E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="str">
+        <f>A20</f>
+        <v>Brokerage commissions %</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3">
+        <f>C20</f>
+        <v>3.7132348098681522E-4</v>
+      </c>
+      <c r="D28" s="3">
+        <f>D20</f>
+        <v>2.0357379527111529E-4</v>
+      </c>
+      <c r="E28" s="3">
+        <f>E20</f>
+        <v>2.0368520628612669E-4</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="8"/>
+        <v>2.5952749418135237E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="str">
+        <f>A15</f>
+        <v>Dividend (gross)</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4">
+        <f>C15</f>
+        <v>4.819646957583102E-2</v>
+      </c>
+      <c r="D30" s="4">
+        <f>D15</f>
+        <v>4.0981274812068293E-2</v>
+      </c>
+      <c r="E30" s="4">
+        <f>E15</f>
+        <v>3.8505771231477227E-2</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="8"/>
+        <v>4.2561171873125518E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="str">
+        <f>A14</f>
+        <v>% tax leakage</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4">
+        <f>C14</f>
+        <v>9.6247189388899757E-2</v>
+      </c>
+      <c r="D31" s="4">
+        <f>D14</f>
+        <v>0.10065396702233163</v>
+      </c>
+      <c r="E31" s="4">
+        <f>E14</f>
+        <v>0.10111295267124767</v>
+      </c>
+      <c r="F31" s="9">
+        <f t="shared" si="8"/>
+        <v>9.9338036360826346E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="str">
+        <f>A18</f>
+        <v>Turnover</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14">
+        <f>C18</f>
+        <v>0.21</v>
+      </c>
+      <c r="D32" s="14">
+        <f>D18</f>
+        <v>0.16</v>
+      </c>
+      <c r="E32" s="14">
+        <f>E18</f>
+        <v>0.11</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="8"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="4">
+        <f>F6+F16+F20-F10</f>
+        <v>6.637604076112337E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A598ED46-EEA8-4CD3-B87C-CF32F0FABA87}">
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="34.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="7"/>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5">
+        <v>274824683</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1056702827</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1668508447</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3452076592</v>
+      </c>
+      <c r="F4" s="5">
+        <v>6666582522</v>
+      </c>
+      <c r="G4" s="5">
+        <v>11757913859</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="5">
+        <v>292899</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2087838</v>
+      </c>
+      <c r="D5" s="5">
+        <v>5061317</v>
+      </c>
+      <c r="E5" s="5">
+        <v>9208685</v>
+      </c>
+      <c r="F5" s="5">
+        <v>18447202</v>
+      </c>
+      <c r="G5" s="5">
+        <v>28367818</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4">
+        <f>0.36%*J6</f>
+        <v>3.3639344262295081E-3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="H6" s="4">
+        <f>AVERAGE(C6:G6)</f>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J6" s="17">
+        <f>342/366</f>
+        <v>0.93442622950819676</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5">
+        <f>B5/B6</f>
+        <v>87070365.49707602</v>
+      </c>
+      <c r="C7" s="5">
+        <f>C5/C6</f>
+        <v>579955000</v>
+      </c>
+      <c r="D7" s="5">
+        <f>D5/D6</f>
+        <v>1405921388.8888888</v>
+      </c>
+      <c r="E7" s="5">
+        <f>E5/E6</f>
+        <v>2557968055.5555558</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" ref="F7:G7" si="0">F5/F6</f>
+        <v>5124222777.7777777</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>7879949444.4444447</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="5">
         <v>25648</v>
@@ -1854,14 +3026,20 @@
       <c r="E9" s="5">
         <v>2622441</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="5">
+        <v>3027604</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2548330</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="16">
-        <f>(B9/B7)/H6</f>
+        <f>(B9/B7)/J6</f>
         <v>3.1523767578585111E-4</v>
       </c>
       <c r="C10" s="16">
@@ -1876,17 +3054,25 @@
         <f>E9/E7</f>
         <v>1.0252047496466649E-3</v>
       </c>
-      <c r="F10" s="4">
-        <f>AVERAGE(B10:E10)</f>
-        <v>6.7682938640859294E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F10" s="16">
+        <f t="shared" ref="F10:G10" si="1">F9/F7</f>
+        <v>5.9084160297046679E-4</v>
+      </c>
+      <c r="G10" s="16">
+        <f t="shared" si="1"/>
+        <v>3.233942067733232E-4</v>
+      </c>
+      <c r="H10" s="4">
+        <f>AVERAGE(C10:G10)</f>
+        <v>6.6126313591846207E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5">
         <v>2054134</v>
@@ -1900,11 +3086,20 @@
       <c r="E12" s="5">
         <v>106217917</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F12" s="5">
+        <v>177008980</v>
+      </c>
+      <c r="G12" s="5">
+        <v>342386807</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="J12" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="5">
         <v>213731</v>
@@ -1919,36 +3114,50 @@
       <c r="E13" s="5">
         <v>10479311</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F13" s="5">
+        <v>19353497</v>
+      </c>
+      <c r="G13" s="5">
+        <v>35268724</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="9">
-        <f t="shared" ref="B14:C14" si="0">B13/(B12+B13)</f>
+        <f t="shared" ref="B14:C14" si="2">B13/(B12+B13)</f>
         <v>9.4243264039085214E-2</v>
       </c>
       <c r="C14" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.4552175767116586E-2</v>
       </c>
       <c r="D14" s="9">
-        <f t="shared" ref="D14:E14" si="1">D13/(D12+D13)</f>
+        <f t="shared" ref="D14:F14" si="3">D13/(D12+D13)</f>
         <v>8.4277342863130308E-2</v>
       </c>
       <c r="E14" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8.9799142444069016E-2</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F14" s="9">
+        <f t="shared" si="3"/>
+        <v>9.8560057377968399E-2</v>
+      </c>
+      <c r="G14" s="9">
+        <f>G13/G12</f>
+        <v>0.10300841994767632</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
-        <f>((B12+B13)/B7)/H6</f>
+        <f>((B12+B13)/B7)/J6</f>
         <v>2.7874161400346192E-2</v>
       </c>
       <c r="C15" s="9">
@@ -1963,14 +3172,22 @@
         <f>(E12+E13)/E7</f>
         <v>4.5621065418135161E-2</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F15" s="9">
+        <f t="shared" ref="F15" si="4">(F12+F13)/F7</f>
+        <v>3.8320441072852131E-2</v>
+      </c>
+      <c r="G15" s="9">
+        <f>G12/G7</f>
+        <v>4.3450381174893325E-2</v>
+      </c>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="10">
-        <f>(B13/B7)/H6</f>
+        <f>(B13/B7)/J6</f>
         <v>2.6269519527209037E-3</v>
       </c>
       <c r="C16" s="10">
@@ -1985,21 +3202,31 @@
         <f>E13/E7</f>
         <v>4.0967325519333103E-3</v>
       </c>
-      <c r="F16" s="4">
-        <f>AVERAGE(B16:E16)</f>
-        <v>3.1724393957065994E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="10">
+        <f t="shared" ref="F16" si="5">F13/F7</f>
+        <v>3.7768648708893632E-3</v>
+      </c>
+      <c r="G16" s="10">
+        <f>G13/G7</f>
+        <v>4.4757551109500205E-3</v>
+      </c>
+      <c r="H16" s="4">
+        <f>AVERAGE(C16:G16)</f>
+        <v>3.6630851223889761E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="14">
         <v>0.32</v>
@@ -2013,14 +3240,20 @@
       <c r="E18" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F18" s="14">
-        <f>AVERAGE(B18:E18)</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="H18" s="4">
+        <f>AVERAGE(C18:G18)</f>
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5">
         <v>28160</v>
@@ -2034,14 +3267,20 @@
       <c r="E19" s="5">
         <v>293289</v>
       </c>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="5">
+        <v>396743</v>
+      </c>
+      <c r="G19" s="5">
+        <v>453186</v>
+      </c>
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
-        <f>(B19/B7)/H6</f>
+        <f>(B19/B7)/J6</f>
         <v>3.4611248245982403E-4</v>
       </c>
       <c r="C20" s="3">
@@ -2056,216 +3295,271 @@
         <f>E19/E7</f>
         <v>1.1465702214811343E-4</v>
       </c>
-      <c r="F20" s="4">
-        <f>AVERAGE(B20:E20)</f>
-        <v>2.2648102925050103E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="3">
+        <f t="shared" ref="F20:G20" si="6">F19/F7</f>
+        <v>7.742501003675246E-5</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="6"/>
+        <v>5.7511282679549058E-5</v>
+      </c>
+      <c r="H20" s="4">
+        <f>AVERAGE(C20:G20)</f>
+        <v>1.3894958545169632E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="19">
-        <f>B3</f>
-        <v>2020</v>
-      </c>
-      <c r="C24" s="19">
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19">
         <f>C3</f>
         <v>2021</v>
       </c>
-      <c r="D24" s="19">
-        <f>D3</f>
+      <c r="D25" s="19">
+        <f t="shared" ref="D25:G25" si="7">D3</f>
         <v>2022</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E25" s="19">
+        <f t="shared" si="7"/>
         <v>2023</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="str">
+      <c r="F25" s="19">
+        <f t="shared" si="7"/>
+        <v>2024</v>
+      </c>
+      <c r="G25" s="19">
+        <f t="shared" si="7"/>
+        <v>2025</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
         <f>A10</f>
         <v>Lending income %</v>
       </c>
-      <c r="B25" s="4">
-        <f>B10</f>
-        <v>3.1523767578585111E-4</v>
-      </c>
-      <c r="C25" s="4">
-        <f t="shared" ref="C25:E25" si="2">C10</f>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4">
+        <f>C10</f>
         <v>6.0258985610952577E-4</v>
       </c>
-      <c r="D25" s="4">
-        <f t="shared" si="2"/>
+      <c r="D26" s="4">
+        <f>D10</f>
         <v>7.6428526409233011E-4</v>
       </c>
-      <c r="E25" s="3">
-        <f t="shared" si="2"/>
+      <c r="E26" s="4">
+        <f>E10</f>
         <v>1.0252047496466649E-3</v>
       </c>
-      <c r="F25" s="9">
-        <f>AVERAGE(B25:E25)</f>
-        <v>6.7682938640859294E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="str">
+      <c r="F26" s="4">
+        <f>F10</f>
+        <v>5.9084160297046679E-4</v>
+      </c>
+      <c r="G26" s="4">
+        <f>G10</f>
+        <v>3.233942067733232E-4</v>
+      </c>
+      <c r="H26" s="9">
+        <f>AVERAGE(C26:G26)</f>
+        <v>6.6126313591846207E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
         <f>A16</f>
         <v>Tax leakage costs</v>
       </c>
-      <c r="B26" s="4">
-        <f>B16</f>
-        <v>2.6269519527209037E-3</v>
-      </c>
-      <c r="C26" s="4">
-        <f t="shared" ref="C26:E26" si="3">C16</f>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
+        <f>C16</f>
         <v>2.4677018044503454E-3</v>
       </c>
-      <c r="D26" s="4">
-        <f t="shared" si="3"/>
+      <c r="D27" s="4">
+        <f>D16</f>
         <v>3.4983712737218396E-3</v>
       </c>
-      <c r="E26" s="4">
-        <f t="shared" si="3"/>
+      <c r="E27" s="4">
+        <f>E16</f>
         <v>4.0967325519333103E-3</v>
       </c>
-      <c r="F26" s="9">
-        <f t="shared" ref="F26:F31" si="4">AVERAGE(B26:E26)</f>
-        <v>3.1724393957065994E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="str">
+      <c r="F27" s="4">
+        <f>F16</f>
+        <v>3.7768648708893632E-3</v>
+      </c>
+      <c r="G27" s="4">
+        <f>G16</f>
+        <v>4.4757551109500205E-3</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" ref="H27:H32" si="8">AVERAGE(C27:G27)</f>
+        <v>3.6630851223889761E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="str">
         <f>A20</f>
         <v>Brokerage commissions %</v>
       </c>
-      <c r="B27" s="3">
-        <f>B20</f>
-        <v>3.4611248245982403E-4</v>
-      </c>
-      <c r="C27" s="3">
-        <f t="shared" ref="C27:E27" si="5">C20</f>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3">
+        <f>C20</f>
         <v>2.0529696269538155E-4</v>
       </c>
-      <c r="D27" s="3">
-        <f t="shared" si="5"/>
+      <c r="D28" s="3">
+        <f>D20</f>
         <v>2.3985764969868515E-4</v>
       </c>
-      <c r="E27" s="3">
-        <f t="shared" si="5"/>
+      <c r="E28" s="3">
+        <f>E20</f>
         <v>1.1465702214811343E-4</v>
       </c>
-      <c r="F27" s="9">
-        <f t="shared" si="4"/>
-        <v>2.2648102925050103E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="str">
+      <c r="F28" s="3">
+        <f>F20</f>
+        <v>7.742501003675246E-5</v>
+      </c>
+      <c r="G28" s="3">
+        <f>G20</f>
+        <v>5.7511282679549058E-5</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="8"/>
+        <v>1.3894958545169632E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="str">
         <f>A15</f>
         <v>Dividend (gross)</v>
       </c>
-      <c r="B29" s="4">
-        <f>B15</f>
-        <v>2.7874161400346192E-2</v>
-      </c>
-      <c r="C29" s="4">
-        <f t="shared" ref="C29:E29" si="6">C15</f>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4">
+        <f>C15</f>
         <v>2.918555060306403E-2</v>
       </c>
-      <c r="D29" s="4">
-        <f t="shared" si="6"/>
+      <c r="D30" s="4">
+        <f>D15</f>
         <v>4.1510222734517523E-2</v>
       </c>
-      <c r="E29" s="4">
-        <f t="shared" si="6"/>
+      <c r="E30" s="4">
+        <f>E15</f>
         <v>4.5621065418135161E-2</v>
       </c>
-      <c r="F29" s="9">
-        <f t="shared" si="4"/>
-        <v>3.6047750039015725E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="str">
+      <c r="F30" s="4">
+        <f>F15</f>
+        <v>3.8320441072852131E-2</v>
+      </c>
+      <c r="G30" s="4">
+        <f>G15</f>
+        <v>4.3450381174893325E-2</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="8"/>
+        <v>3.9617532200692432E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="str">
         <f>A14</f>
         <v>% tax leakage</v>
       </c>
-      <c r="B30" s="4">
-        <f>B14</f>
-        <v>9.4243264039085214E-2</v>
-      </c>
-      <c r="C30" s="4">
-        <f t="shared" ref="C30:E30" si="7">C14</f>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4">
+        <f>C14</f>
         <v>8.4552175767116586E-2</v>
       </c>
-      <c r="D30" s="4">
-        <f t="shared" si="7"/>
+      <c r="D31" s="4">
+        <f>D14</f>
         <v>8.4277342863130308E-2</v>
       </c>
-      <c r="E30" s="4">
-        <f t="shared" si="7"/>
+      <c r="E31" s="4">
+        <f>E14</f>
         <v>8.9799142444069016E-2</v>
       </c>
-      <c r="F30" s="9">
-        <f t="shared" si="4"/>
-        <v>8.8217981278350274E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="str">
+      <c r="F31" s="4">
+        <f>F14</f>
+        <v>9.8560057377968399E-2</v>
+      </c>
+      <c r="G31" s="4">
+        <f>G14</f>
+        <v>0.10300841994767632</v>
+      </c>
+      <c r="H31" s="9">
+        <f t="shared" si="8"/>
+        <v>9.2039427679992139E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="str">
         <f>A18</f>
         <v>Turnover</v>
       </c>
-      <c r="B31" s="14">
-        <f>B18</f>
-        <v>0.32</v>
-      </c>
-      <c r="C31" s="14">
-        <f t="shared" ref="C31:E31" si="8">C18</f>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14">
+        <f>C18</f>
         <v>0.21</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D32" s="14">
+        <f>D18</f>
+        <v>0.21</v>
+      </c>
+      <c r="E32" s="14">
+        <f>E18</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F32" s="14">
+        <f>F18</f>
+        <v>0.08</v>
+      </c>
+      <c r="G32" s="14">
+        <f>G18</f>
+        <v>0.04</v>
+      </c>
+      <c r="H32" s="9">
         <f t="shared" si="8"/>
-        <v>0.21</v>
-      </c>
-      <c r="E31" s="14">
-        <f t="shared" si="8"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F31" s="20">
-        <f t="shared" si="4"/>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="4">
-        <f>E6+F16+F20-F10</f>
-        <v>6.3220910385485074E-3</v>
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="4">
+        <f>H6+H16+H20-H10</f>
+        <v>6.7407715719222105E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2274,288 +3568,622 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E464A6E-318F-4E5F-BBD8-22DF9CD04A86}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="2" max="6" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2022</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="5">
         <v>129555770</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="E4" s="17">
+      <c r="C4" s="5">
+        <v>289259557</v>
+      </c>
+      <c r="D4" s="5">
+        <v>500630776</v>
+      </c>
+      <c r="E4" s="5">
+        <v>776461661</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="H4" s="17">
         <f>338/366</f>
         <v>0.92349726775956287</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5">
         <v>262082</v>
       </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="5">
+        <v>795536</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1404647</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2147216</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4">
+        <f>0.36%*H4</f>
+        <v>3.324590163934426E-3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="F6" s="4">
+        <f>AVERAGE(C6:E6)</f>
+        <v>3.6000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>2</v>
-      </c>
-      <c r="B6" s="4">
-        <f>0.36%*E4</f>
-        <v>3.324590163934426E-3</v>
-      </c>
-      <c r="C6" s="4">
-        <f>AVERAGE(B6:B6)</f>
-        <v>3.324590163934426E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
       </c>
       <c r="B7" s="5">
         <f>B5/B6</f>
         <v>78831370.808678508</v>
       </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="5">
+        <f>C5/C6</f>
+        <v>220982222.22222224</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" ref="D7:E7" si="0">D5/D6</f>
+        <v>390179722.22222221</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>596448888.88888896</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5">
         <v>39408</v>
       </c>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C9" s="5">
+        <v>162572</v>
+      </c>
+      <c r="D9" s="5">
+        <v>321775</v>
+      </c>
+      <c r="E9" s="5">
+        <v>369387</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="16">
-        <f>(B9/B7)/E4</f>
+        <f>(B9/B7)/H4</f>
         <v>5.4131455040788755E-4</v>
       </c>
-      <c r="C10" s="4">
-        <f>AVERAGE(B10:B10)</f>
-        <v>5.4131455040788755E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="16">
+        <f>C9/C7</f>
+        <v>7.3567908931839658E-4</v>
+      </c>
+      <c r="D10" s="16">
+        <f t="shared" ref="D10:E10" si="1">D9/D7</f>
+        <v>8.2468406653059452E-4</v>
+      </c>
+      <c r="E10" s="16">
+        <f t="shared" si="1"/>
+        <v>6.1931040007153447E-4</v>
+      </c>
+      <c r="F10" s="4">
+        <f>AVERAGE(C10:E10)</f>
+        <v>7.2655785197350863E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5">
         <v>4053556</v>
       </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C12" s="5">
+        <v>9936728</v>
+      </c>
+      <c r="D12" s="5">
+        <v>14602870</v>
+      </c>
+      <c r="E12" s="5">
+        <v>26012621</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="H12" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="5">
         <v>581477</v>
       </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C13" s="5">
+        <v>1486596</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2147773</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3686722</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="9">
         <f>B13/(B12+B13)</f>
         <v>0.12545261274299449</v>
       </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C14" s="9">
+        <f t="shared" ref="C14:E14" si="2">C13/(C12+C13)</f>
+        <v>0.130136902358718</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" si="2"/>
+        <v>0.12822033160159882</v>
+      </c>
+      <c r="E14" s="9">
+        <f>E13/E12</f>
+        <v>0.14172820186016627</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
-        <f>((B12+B13)/B7)/E4</f>
+        <f>((B12+B13)/B7)/H4</f>
         <v>6.3667549850810037E-2</v>
       </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C15" s="9">
+        <f>(C12+C13)/C7</f>
+        <v>5.1693407212244316E-2</v>
+      </c>
+      <c r="D15" s="9">
+        <f>(D12+D13)/D7</f>
+        <v>4.2930583128714901E-2</v>
+      </c>
+      <c r="E15" s="9">
+        <f>E12/E7</f>
+        <v>4.3612489661030839E-2</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="10">
-        <f>(B13/B7)/E4</f>
+        <f>(B13/B7)/H4</f>
         <v>7.9872604757289696E-3</v>
       </c>
-      <c r="C16" s="4">
-        <f>AVERAGE(B16:B16)</f>
-        <v>7.9872604757289696E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="10">
+        <f>C13/C7</f>
+        <v>6.7272198869692884E-3</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" ref="D16:E16" si="3">D13/D7</f>
+        <v>5.5045736046138282E-3</v>
+      </c>
+      <c r="E16" s="10">
+        <f>E13/E7</f>
+        <v>6.1811197383029922E-3</v>
+      </c>
+      <c r="F16" s="4">
+        <f>AVERAGE(C16:E16)</f>
+        <v>6.1376377432953684E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="14">
         <v>0.08</v>
       </c>
       <c r="C18" s="14">
-        <f>AVERAGE(B18)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23</v>
+      </c>
+      <c r="D18" s="14">
+        <v>0.17</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0.12</v>
+      </c>
+      <c r="F18" s="4">
+        <f>AVERAGE(C18:E18)</f>
+        <v>0.17333333333333334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5">
         <v>60412</v>
       </c>
-      <c r="C19" s="14"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="5">
+        <v>86612</v>
+      </c>
+      <c r="D19" s="5">
+        <v>104612</v>
+      </c>
+      <c r="E19" s="5">
+        <v>126140</v>
+      </c>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4">
-        <f>(B19/B7)/E4</f>
+        <f>(B19/B7)/H4</f>
         <v>8.2982883219755643E-4</v>
       </c>
       <c r="C20" s="4">
-        <f>AVERAGE(B20:B20)</f>
-        <v>8.2982883219755643E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <f>C19/C7</f>
+        <v>3.9194103095271612E-4</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" ref="D20:E20" si="4">D19/D7</f>
+        <v>2.681123442402255E-4</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="4"/>
+        <v>2.1148501128903657E-4</v>
+      </c>
+      <c r="F20" s="4">
+        <f>AVERAGE(C20:E20)</f>
+        <v>2.9051279549399271E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19">
+        <f>C3</f>
+        <v>2023</v>
+      </c>
+      <c r="D25" s="19">
+        <f t="shared" ref="D25:G25" si="5">D3</f>
+        <v>2024</v>
+      </c>
+      <c r="E25" s="19">
+        <f t="shared" si="5"/>
+        <v>2025</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
+        <f>A10</f>
+        <v>Lending income %</v>
+      </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" s="4">
+        <f>C10</f>
+        <v>7.3567908931839658E-4</v>
+      </c>
+      <c r="D26" s="4">
+        <f>D10</f>
+        <v>8.2468406653059452E-4</v>
+      </c>
+      <c r="E26" s="4">
+        <f>E10</f>
+        <v>6.1931040007153447E-4</v>
+      </c>
+      <c r="F26" s="9">
+        <f>AVERAGE(C26:E26)</f>
+        <v>7.2655785197350863E-4</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
+        <f>A16</f>
+        <v>Tax leakage costs</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
+        <f>C16</f>
+        <v>6.7272198869692884E-3</v>
+      </c>
+      <c r="D27" s="4">
+        <f>D16</f>
+        <v>5.5045736046138282E-3</v>
+      </c>
+      <c r="E27" s="4">
+        <f>E16</f>
+        <v>6.1811197383029922E-3</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" ref="F27:F32" si="6">AVERAGE(C27:E27)</f>
+        <v>6.1376377432953684E-3</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="str">
+        <f>A20</f>
+        <v>Brokerage commissions %</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3">
+        <f>C20</f>
+        <v>3.9194103095271612E-4</v>
+      </c>
+      <c r="D28" s="3">
+        <f>D20</f>
+        <v>2.681123442402255E-4</v>
+      </c>
+      <c r="E28" s="3">
+        <f>E20</f>
+        <v>2.1148501128903657E-4</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="6"/>
+        <v>2.9051279549399271E-4</v>
+      </c>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="str">
+        <f>A15</f>
+        <v>Dividend (gross)</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4">
+        <f>C15</f>
+        <v>5.1693407212244316E-2</v>
+      </c>
+      <c r="D30" s="4">
+        <f>D15</f>
+        <v>4.2930583128714901E-2</v>
+      </c>
+      <c r="E30" s="4">
+        <f>E15</f>
+        <v>4.3612489661030839E-2</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="6"/>
+        <v>4.6078826667330021E-2</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="str">
+        <f>A14</f>
+        <v>% tax leakage</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4">
+        <f>C14</f>
+        <v>0.130136902358718</v>
+      </c>
+      <c r="D31" s="4">
+        <f>D14</f>
+        <v>0.12822033160159882</v>
+      </c>
+      <c r="E31" s="4">
+        <f>E14</f>
+        <v>0.14172820186016627</v>
+      </c>
+      <c r="F31" s="9">
+        <f t="shared" si="6"/>
+        <v>0.13336181194016103</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="str">
+        <f>A18</f>
+        <v>Turnover</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14">
+        <f>C18</f>
+        <v>0.23</v>
+      </c>
+      <c r="D32" s="14">
+        <f>D18</f>
+        <v>0.17</v>
+      </c>
+      <c r="E32" s="14">
+        <f>E18</f>
+        <v>0.12</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="6"/>
+        <v>0.17333333333333334</v>
+      </c>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="4">
+        <f>F6+F16+F20-F10</f>
+        <v>9.3015926868158533E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="11"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="11"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="11"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="11"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="11"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="11"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Avantis/Avantis.xlsx
+++ b/Avantis/Avantis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Avantis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2053" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{442B555B-36A4-4EEA-A1E1-142A46E156D6}"/>
+  <xr:revisionPtr revIDLastSave="2056" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8D1680D-B797-45DE-934F-3CA72CFF2446}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVUV" sheetId="17" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="32">
   <si>
     <t>Net asset value end of year</t>
   </si>
@@ -1618,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D94FFC8-24A2-4765-AFE3-C706492DE4CB}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -1909,14 +1909,14 @@
         <v>3.9739545074896052E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>10</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F19" s="14"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>1.7773645214076005E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1988,223 +1988,82 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19">
-        <f>C3</f>
-        <v>2023</v>
-      </c>
-      <c r="D25" s="19">
-        <f t="shared" ref="D25:G25" si="6">D3</f>
-        <v>2024</v>
-      </c>
-      <c r="E25" s="19">
-        <f t="shared" si="6"/>
-        <v>2025</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="str">
-        <f>A10</f>
-        <v>Lending income %</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="3">
-        <f t="shared" ref="C26:G26" si="7">C10</f>
-        <v>1.1262946611322149E-5</v>
-      </c>
-      <c r="D26" s="3">
-        <f t="shared" si="7"/>
-        <v>1.2729288752210251E-6</v>
-      </c>
-      <c r="E26" s="3">
-        <f t="shared" si="7"/>
-        <v>6.255791098018085E-7</v>
-      </c>
-      <c r="F26" s="9">
-        <f>AVERAGE(C26:E26)</f>
-        <v>4.3871515321149941E-6</v>
-      </c>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="str">
-        <f>A20</f>
-        <v>Brokerage commissions %</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3">
-        <f>C20</f>
-        <v>2.9677616723082272E-5</v>
-      </c>
-      <c r="D27" s="3">
-        <f>D20</f>
-        <v>1.399197567096398E-5</v>
-      </c>
-      <c r="E27" s="3">
-        <f>E20</f>
-        <v>9.6513432481817593E-6</v>
-      </c>
-      <c r="F27" s="9">
-        <f t="shared" ref="F27:F30" si="8">AVERAGE(C27:E27)</f>
-        <v>1.7773645214076005E-5</v>
-      </c>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="str">
-        <f>A15</f>
-        <v>Dividend (gross)</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4">
-        <f>C15</f>
-        <v>2.4668825352249069E-2</v>
-      </c>
-      <c r="D29" s="4">
-        <f>D15</f>
-        <v>2.0612728215785345E-2</v>
-      </c>
-      <c r="E29" s="4">
-        <f>E15</f>
-        <v>1.9185646827968941E-2</v>
-      </c>
-      <c r="F29" s="9">
-        <f t="shared" si="8"/>
-        <v>2.1489066798667786E-2</v>
-      </c>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="str">
-        <f>A18</f>
-        <v>Turnover</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14">
-        <f>C18</f>
-        <v>0.18</v>
-      </c>
-      <c r="D30" s="14">
-        <f>D18</f>
-        <v>0.05</v>
-      </c>
-      <c r="E30" s="14">
-        <f>E18</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F30" s="9">
-        <f t="shared" si="8"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4">
         <f>F6-F10+F20</f>
         <v>1.5133864936819612E-3</v>
       </c>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2214,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFAC02E-C033-44C9-A725-F88F03ADB5EB}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -2471,7 +2330,7 @@
         <v>4.819646957583102E-2</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" ref="D15:E15" si="4">(D12+D13)/D7</f>
+        <f t="shared" ref="D15" si="4">(D12+D13)/D7</f>
         <v>4.0981274812068293E-2</v>
       </c>
       <c r="E15" s="9">
@@ -2493,7 +2352,7 @@
         <v>4.6387747351413532E-3</v>
       </c>
       <c r="D16" s="10">
-        <f t="shared" ref="D16:E16" si="5">D13/D7</f>
+        <f t="shared" ref="D16" si="5">D13/D7</f>
         <v>4.1249278834670318E-3</v>
       </c>
       <c r="E16" s="10">
@@ -2584,242 +2443,65 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F22" s="4"/>
-    </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="4"/>
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="4">
+        <f>F6+F16+F20-F10</f>
+        <v>6.637604076112337E-3</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19">
-        <f>C3</f>
-        <v>2023</v>
-      </c>
-      <c r="D25" s="19">
-        <f t="shared" ref="D25:F25" si="7">D3</f>
-        <v>2024</v>
-      </c>
-      <c r="E25" s="19">
-        <f t="shared" si="7"/>
-        <v>2025</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="str">
-        <f>A10</f>
-        <v>Lending income %</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4">
-        <f>C10</f>
-        <v>3.7054965029438493E-4</v>
-      </c>
-      <c r="D26" s="4">
-        <f>D10</f>
-        <v>3.7861945376396245E-4</v>
-      </c>
-      <c r="E26" s="4">
-        <f>E10</f>
-        <v>2.7373599285533527E-4</v>
-      </c>
-      <c r="F26" s="9">
-        <f>AVERAGE(C26:E26)</f>
-        <v>3.4096836563789418E-4</v>
-      </c>
+      <c r="A26" s="13"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="str">
-        <f>A16</f>
-        <v>Tax leakage costs</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4">
-        <f>C16</f>
-        <v>4.6387747351413532E-3</v>
-      </c>
-      <c r="D27" s="4">
-        <f>D16</f>
-        <v>4.1249278834670318E-3</v>
-      </c>
-      <c r="E27" s="4">
-        <f>E16</f>
-        <v>3.893432224098247E-3</v>
-      </c>
-      <c r="F27" s="9">
-        <f t="shared" ref="F27:F32" si="8">AVERAGE(C27:E27)</f>
-        <v>4.2190449475688774E-3</v>
-      </c>
+      <c r="A27" s="12"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="str">
-        <f>A20</f>
-        <v>Brokerage commissions %</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3">
-        <f>C20</f>
-        <v>3.7132348098681522E-4</v>
-      </c>
-      <c r="D28" s="3">
-        <f>D20</f>
-        <v>2.0357379527111529E-4</v>
-      </c>
-      <c r="E28" s="3">
-        <f>E20</f>
-        <v>2.0368520628612669E-4</v>
-      </c>
-      <c r="F28" s="9">
-        <f t="shared" si="8"/>
-        <v>2.5952749418135237E-4</v>
-      </c>
+      <c r="A28" s="12"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F29" s="9"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="str">
-        <f>A15</f>
-        <v>Dividend (gross)</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4">
-        <f>C15</f>
-        <v>4.819646957583102E-2</v>
-      </c>
-      <c r="D30" s="4">
-        <f>D15</f>
-        <v>4.0981274812068293E-2</v>
-      </c>
-      <c r="E30" s="4">
-        <f>E15</f>
-        <v>3.8505771231477227E-2</v>
-      </c>
-      <c r="F30" s="9">
-        <f t="shared" si="8"/>
-        <v>4.2561171873125518E-2</v>
-      </c>
+      <c r="A30" s="12"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="str">
-        <f>A14</f>
-        <v>% tax leakage</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4">
-        <f>C14</f>
-        <v>9.6247189388899757E-2</v>
-      </c>
-      <c r="D31" s="4">
-        <f>D14</f>
-        <v>0.10065396702233163</v>
-      </c>
-      <c r="E31" s="4">
-        <f>E14</f>
-        <v>0.10111295267124767</v>
-      </c>
-      <c r="F31" s="9">
-        <f t="shared" si="8"/>
-        <v>9.9338036360826346E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="str">
-        <f>A18</f>
-        <v>Turnover</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14">
-        <f>C18</f>
-        <v>0.21</v>
-      </c>
-      <c r="D32" s="14">
-        <f>D18</f>
-        <v>0.16</v>
-      </c>
-      <c r="E32" s="14">
-        <f>E18</f>
-        <v>0.11</v>
-      </c>
-      <c r="F32" s="9">
-        <f t="shared" si="8"/>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="4">
-        <f>F6+F16+F20-F10</f>
-        <v>6.637604076112337E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3801,7 +3483,7 @@
         <v>0.12545261274299449</v>
       </c>
       <c r="C14" s="9">
-        <f t="shared" ref="C14:E14" si="2">C13/(C12+C13)</f>
+        <f t="shared" ref="C14:D14" si="2">C13/(C12+C13)</f>
         <v>0.130136902358718</v>
       </c>
       <c r="D14" s="9">
@@ -3849,7 +3531,7 @@
         <v>6.7272198869692884E-3</v>
       </c>
       <c r="D16" s="10">
-        <f t="shared" ref="D16:E16" si="3">D13/D7</f>
+        <f t="shared" ref="D16" si="3">D13/D7</f>
         <v>5.5045736046138282E-3</v>
       </c>
       <c r="E16" s="10">
@@ -3966,7 +3648,7 @@
         <v>2023</v>
       </c>
       <c r="D25" s="19">
-        <f t="shared" ref="D25:G25" si="5">D3</f>
+        <f t="shared" ref="D25:E25" si="5">D3</f>
         <v>2024</v>
       </c>
       <c r="E25" s="19">

--- a/Avantis/Avantis.xlsx
+++ b/Avantis/Avantis.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2056" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8D1680D-B797-45DE-934F-3CA72CFF2446}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVUV" sheetId="17" r:id="rId1"/>
